--- a/mock-portal/MockData/quality_002.xlsx
+++ b/mock-portal/MockData/quality_002.xlsx
@@ -55,7 +55,9 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -445,7 +447,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ACME</t>
+          <t>勝宏科技</t>
         </is>
       </c>
     </row>
@@ -457,7 +459,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOT-99123</t>
+          <t>LOT-26-99123</t>
         </is>
       </c>
     </row>
@@ -469,7 +471,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>

--- a/mock-portal/MockData/quality_002.xlsx
+++ b/mock-portal/MockData/quality_002.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>勝宏科技</t>
+          <t>百辰光電</t>
         </is>
       </c>
     </row>
